--- a/docs/Lab01/Lab01_ReviewReport.xlsx
+++ b/docs/Lab01/Lab01_ReviewReport.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Laptop\e\VVSS\CamiVVSS_ro2025-2026\Labs\CheckListsAll\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anama\Desktop\cs_ubb\an-III\VVSS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFE83867-3721-469D-B0A3-67FDA22FF09F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6873695-9735-4E2F-9CD9-CB3360B50126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="650" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements Phase Defects" sheetId="7" r:id="rId1"/>
@@ -18,8 +18,11 @@
     <sheet name="Coding Phase Defects" sheetId="5" r:id="rId3"/>
     <sheet name="Tool-basedCodeAnalysis" sheetId="8" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -36,18 +39,69 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="101">
+  <si>
+    <t>do not print this form</t>
+  </si>
+  <si>
+    <t>Echipa</t>
+  </si>
+  <si>
+    <t>Review Form. Requirements Defects</t>
+  </si>
+  <si>
+    <t>Numele si prenumele</t>
+  </si>
+  <si>
+    <t>Grupa</t>
+  </si>
+  <si>
+    <t>Student 1:</t>
+  </si>
+  <si>
+    <t>Oanea Raul-Emmanuel</t>
+  </si>
+  <si>
+    <t>235/1</t>
+  </si>
   <si>
     <t>Document  Title:</t>
   </si>
   <si>
+    <t>Requirements Document</t>
+  </si>
+  <si>
+    <t>Student 2:</t>
+  </si>
+  <si>
+    <t>Ordean Anamaria</t>
+  </si>
+  <si>
+    <t>Author Name:</t>
+  </si>
+  <si>
+    <t>Firicescu George</t>
+  </si>
+  <si>
+    <t>Student 3:</t>
+  </si>
+  <si>
+    <t>Mierla Constantin</t>
+  </si>
+  <si>
+    <t>234/1</t>
+  </si>
+  <si>
+    <t>Reviewer Name:</t>
+  </si>
+  <si>
+    <t>Oanea Raul-Emmanuel, Ordean Anamaria</t>
+  </si>
+  <si>
     <t xml:space="preserve">Review date: </t>
   </si>
   <si>
-    <t>Reviewer Name:</t>
-  </si>
-  <si>
-    <t>do not print this form</t>
+    <t>14.03.2026</t>
   </si>
   <si>
     <t>Crt. No.</t>
@@ -62,76 +116,234 @@
     <t>Comments/ improvements</t>
   </si>
   <si>
+    <t>R01</t>
+  </si>
+  <si>
+    <t>Punctul 2 - functionale</t>
+  </si>
+  <si>
+    <t>Fiecare produs trebuie sa apartina unui tip si categorii, dar nu avem o diferenta clara intre ce inseamna tipul/ categoria unui produs</t>
+  </si>
+  <si>
+    <t>R02</t>
+  </si>
+  <si>
+    <t>Punctul 5 - functionale</t>
+  </si>
+  <si>
+    <t>Lipseste gestionarea erorilor, ce se intampla daca un ingredient lipeste din stoc, se blocheaza aplicatia/ emite o eroare?</t>
+  </si>
+  <si>
+    <t>R04</t>
+  </si>
+  <si>
+    <t>Punctul 5 - non-functionale</t>
+  </si>
+  <si>
+    <t>Nu se specifica daca la inceputul aplicatiei sunt create automate fisierele text sau aplicatia nu functioneaza</t>
+  </si>
+  <si>
+    <t>R05</t>
+  </si>
+  <si>
+    <t>Punctul 3 - functionale</t>
+  </si>
+  <si>
+    <t>nu este definita exact functia de stergere, ce se intampla daca sterg un produs dintr-o anumita categorie, se sterg toate sau doar produsul selectat</t>
+  </si>
+  <si>
     <t>Effort to review document (hours):</t>
   </si>
   <si>
-    <t>Author Name:</t>
+    <t>Review Form. Architectural Design Defects</t>
+  </si>
+  <si>
+    <t>235./1</t>
+  </si>
+  <si>
+    <t>Architectural Design Document</t>
   </si>
   <si>
     <t xml:space="preserve">Author Name: </t>
   </si>
   <si>
+    <t>Georgescu Calin</t>
+  </si>
+  <si>
+    <t>A02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se oberva ca arhitectura stratificata nu este respectata intrucat mai multe clase din modelul de date pot fi accesate direct din controllerul viewului (ex: Order, Reteta =&gt; DrinkShopController). Ar trebui accesate printr-un layer intermediar.  </t>
+  </si>
+  <si>
+    <t>A05</t>
+  </si>
+  <si>
+    <t>Nu exista un mod specific de a gestiona erorile posibile</t>
+  </si>
+  <si>
+    <t>A07</t>
+  </si>
+  <si>
+    <t>Numele nu sugereaza rolul si layerul din care face parte clasa numita. Se oberva si inconsistenta deoarece denumiere sunt atat in engleza cat si in romana</t>
+  </si>
+  <si>
+    <t>A09</t>
+  </si>
+  <si>
+    <t>Unele relatii de agregare nu au denumiri sugestive (ex: DrinkShopController - Reteta)</t>
+  </si>
+  <si>
+    <t>Review Form. Coding Defects</t>
+  </si>
+  <si>
+    <t>Coding Document</t>
+  </si>
+  <si>
     <t>Popescu Ionel</t>
   </si>
   <si>
-    <t>Georgescu Anca</t>
-  </si>
-  <si>
-    <t>Firicescu George</t>
-  </si>
-  <si>
-    <t>Requirements Document</t>
-  </si>
-  <si>
-    <t>Architectural Design Document</t>
-  </si>
-  <si>
-    <t>Coding Document</t>
-  </si>
-  <si>
-    <t>Review Form. Coding Defects</t>
-  </si>
-  <si>
-    <t>Review Form. Architectural Design Defects</t>
-  </si>
-  <si>
-    <t>Review Form. Requirements Defects</t>
-  </si>
-  <si>
-    <t>Student 1:</t>
-  </si>
-  <si>
-    <t>Student 2:</t>
-  </si>
-  <si>
-    <t>Student 3:</t>
-  </si>
-  <si>
-    <t>Echipa</t>
-  </si>
-  <si>
-    <t>Grupa</t>
+    <t>Mirela Constantyn</t>
+  </si>
+  <si>
+    <t>214/1</t>
+  </si>
+  <si>
+    <t>15.03.2026</t>
+  </si>
+  <si>
+    <t>C06</t>
+  </si>
+  <si>
+    <t>DrinkShopController.java
+onAddProduct() / onUpdateProduct()</t>
+  </si>
+  <si>
+    <t>Double.parseDouble() este apelat fara validare pe input — daca utilizatorul introduce text invalid (ex: "abc"), apare NumberFormatException la procesarea datelor de intrare.</t>
+  </si>
+  <si>
+    <t>C01</t>
+  </si>
+  <si>
+    <t>DrinkShopController.java
+onUpdateProduct()</t>
+  </si>
+  <si>
+    <t>Nu exista logica de decizie pentru campuri goale — se poate salva un produs cu nume gol sau pret 0 fara niciun avertisment catre utilizator.</t>
+  </si>
+  <si>
+    <t>C04</t>
+  </si>
+  <si>
+    <t>FileProductRepository.java
+extractEntity()</t>
+  </si>
+  <si>
+    <t>Nu exista tratarea erorilor la citirea/parsarea liniilor din fisier — o linie corupta in products.txt provoaca ArrayIndexOutOfBoundsException si opreste aplicatia.</t>
+  </si>
+  <si>
+    <t>C08</t>
+  </si>
+  <si>
+    <t>DrinkShopController.java
+onFinalizeOrder()</t>
+  </si>
+  <si>
+    <t>Nu exista mesaj de eroare afisat utilizatorului daca stocul este insuficient la finalizarea comenzii — exceptia este aruncata fara feedback vizibil.</t>
+  </si>
+  <si>
+    <t>C05</t>
+  </si>
+  <si>
+    <t>DrinkShopService.java + DrinkShopController.java
+onFinalizeOrder()</t>
+  </si>
+  <si>
+    <t>Metoda comandaProdus() nu este apelata la finalizarea comenzii (onFinalizeOrder()), deci subprogramul de consum stoc nu este invocat corect.</t>
+  </si>
+  <si>
+    <t>Tool-based Code Analysis</t>
   </si>
   <si>
     <t>Tool used:</t>
   </si>
   <si>
+    <t>SonarQube</t>
+  </si>
+  <si>
+    <t>15.02.2026</t>
+  </si>
+  <si>
+    <t>File, Line</t>
+  </si>
+  <si>
+    <t>Issue</t>
+  </si>
+  <si>
     <t>Before</t>
   </si>
   <si>
-    <t>Issue</t>
-  </si>
-  <si>
-    <t>File, Line</t>
-  </si>
-  <si>
     <t>After/Argument</t>
   </si>
   <si>
-    <t>Numele si prenumele</t>
-  </si>
-  <si>
-    <t>Tool-based Code Analysis</t>
+    <t>DailyReportService, lines 6, 7, 8</t>
+  </si>
+  <si>
+    <t>Unused imports</t>
+  </si>
+  <si>
+    <t>librarii utilitare nefolosite erau importate in fisiere</t>
+  </si>
+  <si>
+    <t>Unused Imports</t>
+  </si>
+  <si>
+    <t>DailyReportService, line 23</t>
+  </si>
+  <si>
+    <t>Comentarii nesugestive</t>
+  </si>
+  <si>
+    <t>comentarii cu cod au fost lasate in fisier</t>
+  </si>
+  <si>
+    <t>comentariile au fost sterse</t>
+  </si>
+  <si>
+    <t>AbstractRepository, line 20</t>
+  </si>
+  <si>
+    <t>Unnecesary cast</t>
+  </si>
+  <si>
+    <t>Functia face cast la List&lt;E&gt;, desi elementul returnat este deja de acest tip</t>
+  </si>
+  <si>
+    <t>Sters castul inutil</t>
+  </si>
+  <si>
+    <t>AbstractRepository, line 8</t>
+  </si>
+  <si>
+    <t>Rename to match generic match</t>
+  </si>
+  <si>
+    <t>Se foloseste ID pentru declarearea clasei generice</t>
+  </si>
+  <si>
+    <t>Clasa nu a fost modificata intrucat acest name este sugestiv tipului pe care il reprezinta</t>
+  </si>
+  <si>
+    <t>CsvExporter, line 14</t>
+  </si>
+  <si>
+    <t>Add a private constructor to implicitly hide the public one</t>
+  </si>
+  <si>
+    <t>Era declarat constructor ul public al clasei utilitare, desi nu era necesar</t>
+  </si>
+  <si>
+    <t>Added private constructor to prevent instantiation of utility class</t>
   </si>
   <si>
     <t>Effort to perform tool-based code analysis (hours):</t>
@@ -141,34 +353,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -326,77 +517,74 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -707,172 +895,297 @@
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J27"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.90625" style="6"/>
-    <col min="2" max="2" width="12.26953125" style="6" customWidth="1"/>
-    <col min="3" max="4" width="16.26953125" style="6" customWidth="1"/>
-    <col min="5" max="5" width="41.453125" style="6" customWidth="1"/>
-    <col min="6" max="8" width="8.90625" style="6"/>
-    <col min="9" max="9" width="21" style="6" customWidth="1"/>
-    <col min="10" max="10" width="14.453125" style="6" customWidth="1"/>
-    <col min="11" max="16384" width="8.90625" style="6"/>
+    <col min="1" max="1" width="8.88671875" style="5"/>
+    <col min="2" max="2" width="12.33203125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="23.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.44140625" style="5" customWidth="1"/>
+    <col min="6" max="8" width="8.88671875" style="5"/>
+    <col min="9" max="9" width="21" style="5" customWidth="1"/>
+    <col min="10" max="10" width="14.44140625" style="5" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="4"/>
-      <c r="B1" s="5" t="s">
+    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="3"/>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="17"/>
+      <c r="B2" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="J2" s="16" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="22"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="24"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="17"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="19"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="19"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="17"/>
+      <c r="B9" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B2" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2" s="17" t="s">
+      <c r="E9" s="13" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="H3" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C4" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="25"/>
-      <c r="H4" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C5" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="27"/>
-      <c r="H5" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B6" s="8"/>
-      <c r="C6" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C7" s="9" t="s">
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+    </row>
+    <row r="10" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="17"/>
+      <c r="B10" s="16">
         <v>1</v>
       </c>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B9" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B10" s="3">
-        <v>1</v>
-      </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B11" s="3">
+      <c r="C10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+    </row>
+    <row r="11" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="17"/>
+      <c r="B11" s="16">
         <f>B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B12" s="3">
+      <c r="C11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+    </row>
+    <row r="12" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="17"/>
+      <c r="B12" s="16">
         <f t="shared" ref="B12:B25" si="0">B11+1</f>
         <v>3</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B13" s="3">
+      <c r="C12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+    </row>
+    <row r="13" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="17"/>
+      <c r="B13" s="16">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B14" s="3">
+      <c r="C13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="17"/>
+      <c r="B14" s="16">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="2"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B15" s="3">
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="17"/>
+      <c r="B15" s="16">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="2"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B16" s="3">
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="17"/>
+      <c r="B16" s="16">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B17" s="3">
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B17" s="16">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -880,83 +1193,84 @@
       <c r="D17" s="1"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B18" s="3">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B18" s="16">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="15"/>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B19" s="3">
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="18"/>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B19" s="16">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="15"/>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B20" s="3">
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="18"/>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="16">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="15"/>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B21" s="3">
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="18"/>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B21" s="16">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="15"/>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B22" s="3">
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="18"/>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="16">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="15"/>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B23" s="3">
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="18"/>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B23" s="16">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="15"/>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B24" s="3">
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="18"/>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B24" s="16">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="15"/>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B25" s="3">
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="18"/>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B25" s="16">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="15"/>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="C27" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="12"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="18"/>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B27" s="17"/>
+      <c r="C27" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D27" s="11"/>
       <c r="E27" s="1"/>
     </row>
   </sheetData>
@@ -979,171 +1293,287 @@
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J28"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.90625" style="6"/>
-    <col min="2" max="2" width="12.26953125" style="6" customWidth="1"/>
-    <col min="3" max="4" width="16.26953125" style="6" customWidth="1"/>
-    <col min="5" max="5" width="41.453125" style="6" customWidth="1"/>
-    <col min="6" max="8" width="8.90625" style="6"/>
-    <col min="9" max="9" width="22.08984375" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="8.90625" style="6"/>
+    <col min="1" max="1" width="8.88671875" style="5"/>
+    <col min="2" max="2" width="12.33203125" style="5" customWidth="1"/>
+    <col min="3" max="4" width="16.33203125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="41.44140625" style="5" customWidth="1"/>
+    <col min="6" max="8" width="8.88671875" style="5"/>
+    <col min="9" max="9" width="22.109375" style="5" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="4"/>
-      <c r="B1" s="5" t="s">
+    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="3"/>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="17"/>
+      <c r="B2" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="J2" s="16" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" s="25"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="27"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="17"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="19"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="19"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="17"/>
+      <c r="B9" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B2" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2" s="17" t="s">
+      <c r="E9" s="9" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="H3" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C4" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="28"/>
-      <c r="H4" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C5" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="30"/>
-      <c r="H5" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B6" s="8"/>
-      <c r="C6" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C7" s="9" t="s">
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+    </row>
+    <row r="10" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="17"/>
+      <c r="B10" s="16">
         <v>1</v>
       </c>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B9" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B10" s="3">
-        <v>1</v>
-      </c>
-      <c r="C10" s="1"/>
+      <c r="C10" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B11" s="3">
+      <c r="E10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+    </row>
+    <row r="11" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="17"/>
+      <c r="B11" s="16">
         <f>B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B12" s="3">
+      <c r="E11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+    </row>
+    <row r="12" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="17"/>
+      <c r="B12" s="16">
         <f t="shared" ref="B12:B26" si="0">B11+1</f>
         <v>3</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B13" s="3">
+      <c r="C12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+    </row>
+    <row r="13" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="17"/>
+      <c r="B13" s="16">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B14" s="3">
+      <c r="C13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="17"/>
+      <c r="B14" s="16">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B15" s="3">
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="17"/>
+      <c r="B15" s="16">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="2"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B16" s="3">
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="17"/>
+      <c r="B16" s="16">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B17" s="3">
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B17" s="16">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -1151,8 +1581,8 @@
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B18" s="3">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B18" s="16">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -1160,8 +1590,8 @@
       <c r="D18" s="1"/>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B19" s="3">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B19" s="16">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -1169,8 +1599,8 @@
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B20" s="3">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="16">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
@@ -1178,8 +1608,8 @@
       <c r="D20" s="1"/>
       <c r="E20" s="2"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B21" s="3">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B21" s="16">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -1187,8 +1617,8 @@
       <c r="D21" s="1"/>
       <c r="E21" s="2"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B22" s="3">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="16">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
@@ -1196,8 +1626,8 @@
       <c r="D22" s="1"/>
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B23" s="3">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B23" s="16">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
@@ -1205,8 +1635,8 @@
       <c r="D23" s="1"/>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B24" s="3">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B24" s="16">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
@@ -1214,8 +1644,8 @@
       <c r="D24" s="1"/>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B25" s="3">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B25" s="16">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
@@ -1223,8 +1653,8 @@
       <c r="D25" s="1"/>
       <c r="E25" s="2"/>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B26" s="3">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B26" s="16">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
@@ -1232,11 +1662,12 @@
       <c r="D26" s="1"/>
       <c r="E26" s="2"/>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="C28" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" s="12"/>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B28" s="17"/>
+      <c r="C28" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D28" s="11"/>
       <c r="E28" s="1"/>
     </row>
   </sheetData>
@@ -1259,172 +1690,302 @@
     <tabColor theme="3" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.90625" style="6"/>
-    <col min="2" max="2" width="12.26953125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="16.26953125" style="6" customWidth="1"/>
-    <col min="4" max="4" width="18" style="6" customWidth="1"/>
-    <col min="5" max="5" width="41.453125" style="6" customWidth="1"/>
-    <col min="6" max="8" width="8.90625" style="6"/>
-    <col min="9" max="9" width="26.7265625" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="8.90625" style="6"/>
+    <col min="1" max="1" width="8.88671875" style="5"/>
+    <col min="2" max="2" width="12.33203125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="18" style="5" customWidth="1"/>
+    <col min="5" max="5" width="41.44140625" style="5" customWidth="1"/>
+    <col min="6" max="8" width="8.88671875" style="5"/>
+    <col min="9" max="9" width="26.6640625" style="5" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="4"/>
-      <c r="B1" s="5" t="s">
+    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="3"/>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="17"/>
+      <c r="B2" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="J2" s="16" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" s="28"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5" s="30"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="J5" s="16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="17"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="19"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="E7" s="19"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="17"/>
+      <c r="B9" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B2" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2" s="17" t="s">
+      <c r="E9" s="9" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="H3" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C4" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="31"/>
-      <c r="H4" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C5" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="33"/>
-      <c r="H5" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B6" s="8"/>
-      <c r="C6" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C7" s="9" t="s">
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+    </row>
+    <row r="10" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="17"/>
+      <c r="B10" s="16">
         <v>1</v>
       </c>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B9" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B10" s="3">
-        <v>1</v>
-      </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B11" s="3">
+      <c r="C10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+    </row>
+    <row r="11" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="17"/>
+      <c r="B11" s="16">
         <f>B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B12" s="3">
+      <c r="C11" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+    </row>
+    <row r="12" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="17"/>
+      <c r="B12" s="16">
         <f t="shared" ref="B12:B30" si="0">B11+1</f>
         <v>3</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B13" s="3">
+      <c r="C12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+    </row>
+    <row r="13" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="17"/>
+      <c r="B13" s="16">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B14" s="3">
+      <c r="C13" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+    </row>
+    <row r="14" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+      <c r="A14" s="17"/>
+      <c r="B14" s="16">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B15" s="3">
+      <c r="C14" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="17"/>
+      <c r="B15" s="16">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B16" s="3">
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="17"/>
+      <c r="B16" s="16">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B17" s="3">
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B17" s="16">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -1432,8 +1993,8 @@
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B18" s="3">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B18" s="16">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -1441,8 +2002,8 @@
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B19" s="3">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B19" s="16">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -1450,8 +2011,8 @@
       <c r="D19" s="1"/>
       <c r="E19" s="2"/>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B20" s="3">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="16">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
@@ -1459,8 +2020,8 @@
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B21" s="3">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B21" s="16">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -1468,8 +2029,8 @@
       <c r="D21" s="1"/>
       <c r="E21" s="2"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B22" s="3">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="16">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
@@ -1477,8 +2038,8 @@
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B23" s="3">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B23" s="16">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
@@ -1486,8 +2047,8 @@
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B24" s="3">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B24" s="16">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
@@ -1495,8 +2056,8 @@
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B25" s="3">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B25" s="16">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
@@ -1504,8 +2065,8 @@
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B26" s="3">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B26" s="16">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
@@ -1513,8 +2074,8 @@
       <c r="D26" s="1"/>
       <c r="E26" s="2"/>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B27" s="3">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B27" s="16">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
@@ -1522,8 +2083,8 @@
       <c r="D27" s="2"/>
       <c r="E27" s="1"/>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B28" s="3">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B28" s="16">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
@@ -1531,8 +2092,8 @@
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B29" s="3">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B29" s="16">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
@@ -1540,8 +2101,8 @@
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B30" s="3">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B30" s="16">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
@@ -1549,11 +2110,12 @@
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="C32" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="12"/>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B32" s="17"/>
+      <c r="C32" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D32" s="11"/>
       <c r="E32" s="1"/>
     </row>
   </sheetData>
@@ -1576,153 +2138,270 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:J35"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.90625" style="6"/>
-    <col min="2" max="2" width="12.26953125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="16.26953125" style="6" customWidth="1"/>
-    <col min="4" max="4" width="18" style="6" customWidth="1"/>
-    <col min="5" max="5" width="23.90625" style="6" customWidth="1"/>
-    <col min="6" max="6" width="16.6328125" style="6" customWidth="1"/>
-    <col min="7" max="8" width="8.90625" style="6"/>
-    <col min="9" max="9" width="26.7265625" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="8.90625" style="6"/>
+    <col min="1" max="1" width="8.88671875" style="5"/>
+    <col min="2" max="2" width="12.33203125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="18" style="5" customWidth="1"/>
+    <col min="5" max="5" width="23.88671875" style="5" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" style="5" customWidth="1"/>
+    <col min="7" max="8" width="8.88671875" style="5"/>
+    <col min="9" max="9" width="26.6640625" style="5" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="4"/>
-      <c r="B1" s="5" t="s">
+    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="3"/>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="17"/>
+      <c r="B2" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B2" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2" s="17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="H3" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C4" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="H4" s="17" t="s">
+      <c r="J2" s="16" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4" s="28"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="19"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="17"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" s="19"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="17"/>
+      <c r="B9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C5" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="H5" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B6" s="8"/>
-      <c r="C6" s="9" t="s">
+      <c r="C9" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+    </row>
+    <row r="10" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="17"/>
+      <c r="B10" s="16">
         <v>1</v>
       </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="20"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B9" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B10" s="3">
-        <v>1</v>
-      </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B11" s="3">
+      <c r="C10" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+    </row>
+    <row r="11" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="17"/>
+      <c r="B11" s="16">
         <f>B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B12" s="3">
+      <c r="C11" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+    </row>
+    <row r="12" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="17"/>
+      <c r="B12" s="16">
         <f t="shared" ref="B12:B30" si="0">B11+1</f>
         <v>3</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B13" s="3">
+      <c r="C12" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+    </row>
+    <row r="13" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+      <c r="A13" s="17"/>
+      <c r="B13" s="16">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B14" s="3">
+      <c r="C13" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+    </row>
+    <row r="14" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+      <c r="A14" s="17"/>
+      <c r="B14" s="16">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B15" s="3">
+      <c r="C14" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="17"/>
+      <c r="B15" s="16">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -1730,9 +2409,14 @@
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B16" s="3">
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="17"/>
+      <c r="B16" s="16">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -1740,9 +2424,13 @@
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B17" s="3">
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B17" s="16">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -1751,8 +2439,8 @@
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B18" s="3">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B18" s="16">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -1761,8 +2449,8 @@
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B19" s="3">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B19" s="16">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -1771,8 +2459,8 @@
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B20" s="3">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B20" s="16">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
@@ -1781,8 +2469,8 @@
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B21" s="3">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B21" s="16">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -1791,8 +2479,8 @@
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B22" s="3">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B22" s="16">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
@@ -1801,8 +2489,8 @@
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B23" s="3">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B23" s="16">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
@@ -1811,8 +2499,8 @@
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B24" s="3">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B24" s="16">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
@@ -1821,8 +2509,8 @@
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="3">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B25" s="16">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
@@ -1831,8 +2519,8 @@
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B26" s="3">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B26" s="16">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
@@ -1841,8 +2529,8 @@
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B27" s="3">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B27" s="16">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
@@ -1851,8 +2539,8 @@
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B28" s="3">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B28" s="16">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
@@ -1861,8 +2549,8 @@
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B29" s="3">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B29" s="16">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
@@ -1871,8 +2559,8 @@
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B30" s="3">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B30" s="16">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
@@ -1881,16 +2569,17 @@
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="C32" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="D32" s="35"/>
-      <c r="E32" s="35"/>
-      <c r="F32" s="18"/>
-    </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F35" s="21"/>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B32" s="17"/>
+      <c r="C32" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="15"/>
+    </row>
+    <row r="35" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F35" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1904,4 +2593,254 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="3c621349-07bb-4f69-bb8c-ca817af798a6" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D80DCAE733D3F841B4052C53207B64B5" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9b18399ff56830746ac2afd8a8ebc386">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="3c621349-07bb-4f69-bb8c-ca817af798a6" xmlns:ns4="cb3df994-17ae-497d-bc9c-e030f194ba7e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="af3550412e37827ab91d53340e020360" ns3:_="" ns4:_="">
+    <xsd:import namespace="3c621349-07bb-4f69-bb8c-ca817af798a6"/>
+    <xsd:import namespace="cb3df994-17ae-497d-bc9c-e030f194ba7e"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns3:_activity" minOccurs="0"/>
+                <xsd:element ref="ns4:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns4:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns4:SharingHintHash" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3c621349-07bb-4f69-bb8c-ca817af798a6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="_activity" ma:index="8" nillable="true" ma:displayName="_activity" ma:hidden="true" ma:internalName="_activity">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceMetadata" ma:index="12" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="13" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="14" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="15" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="cb3df994-17ae-497d-bc9c-e030f194ba7e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="9" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="10" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="SharingHintHash" ma:index="11" nillable="true" ma:displayName="Sharing Hint Hash" ma:hidden="true" ma:internalName="SharingHintHash" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51C24E5F-0C27-402A-ACA4-3988E3D19F50}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="3c621349-07bb-4f69-bb8c-ca817af798a6"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="cb3df994-17ae-497d-bc9c-e030f194ba7e"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D398A91-9605-4744-80D6-44CB6E0B1A53}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{539296E5-CA9C-4BEA-84A1-EFB10204AEAD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3c621349-07bb-4f69-bb8c-ca817af798a6"/>
+    <ds:schemaRef ds:uri="cb3df994-17ae-497d-bc9c-e030f194ba7e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>